--- a/data/outputs/3. Digital Security IT Sample Register (Final).xlsx
+++ b/data/outputs/3. Digital Security IT Sample Register (Final).xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Identity and Access Management systems are compromised due to outdated operating systems.</t>
+          <t>Identity and Access Management (IAM) systems are compromised due to vulnerabilities from outdated operating systems supporting web applications.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -530,7 +530,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -539,12 +539,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Implement automated IAM systems and multifactor authentication; update application architecture; implement data encryption; adopt ISO 27001 framework.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>Implement automated IAM systems, multi-factor authentication, update application architecture, and enforce data encryption with an ISO 27001 framework.</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,12 +562,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>ICT-002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Backup and recovery services are undocumented and untested, with critical systems on outdated infrastructure risking database corruption.</t>
+          <t>Backup and recovery services are undocumented and untested, with critical systems running on outdated infrastructure and operating systems leading to database corruptions.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -574,14 +582,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -590,12 +598,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Implement automated IAM and MFA, update application architecture, implement data encryption, and adopt ISO 27001 framework.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>Implement automated IAM systems, multi-factor authentication, update application architecture, implement data encryption, and deploy an ISO 27001-based security framework.</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -610,7 +626,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Critical systems face outages and cyber intrusions due to outdated infrastructure and lack of disaster recovery.</t>
+          <t>Critical systems are vulnerable due to outdated infrastructure and operating systems, leading to outages and security breaches, with no high-availability architecture or adequate disaster recovery.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -625,14 +641,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -641,12 +657,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Document and test backup and recovery services; migrate systems to new infrastructure; implement ISO 27001 framework and controls.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>Migrate systems to new infrastructure and implement an ISO 27001-based security framework with tested backup and recovery services.</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outputs/3. Digital Security IT Sample Register (Final).xlsx
+++ b/data/outputs/3. Digital Security IT Sample Register (Final).xlsx
@@ -431,99 +431,99 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Risk ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Project Stage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Project Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Owner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mitigating Action</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Date Added</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (post-mitigation)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>ICT-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICT-001</t>
+          <t>Identity and Access Management (IAM) systems compromised Systems are susceptible to intrusion from external sources due to web applications supported by out of date operating systems</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Identity and Access Management (IAM) systems are compromised due to vulnerabilities from outdated operating systems supporting web applications.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Uaa Lead</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Implement automated IAM systems and Multiform Authentication where required Complete Update of new Application Architecture. Data encryption at rest and in transit implemented for all systems. ISO 27001 based Framework and associated relevant controls implemented.</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -537,52 +537,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Implement automated IAM systems, multi-factor authentication, update application architecture, and enforce data encryption with an ISO 27001 framework.</t>
-        </is>
+      <c r="J2" t="n">
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
         <v>5</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>ICT-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICT-002</t>
+          <t>Backup and recovery services are not documented and untested. Critical Systems are supported by out of date infrastructure and operating systems, resulting in database corruptions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Backup and recovery services are undocumented and untested, with critical systems running on outdated infrastructure and operating systems leading to database corruptions.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Infrastructure Manager</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Implement automated IAM systems and Multiform Authentication where required Complete Update of new Application Architecture. Data encryption at rest and in transit implemented for all systems. ISO 27001 based Framework and associated relevant controls implemented.</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -596,52 +596,52 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Implement automated IAM systems, multi-factor authentication, update application architecture, implement data encryption, and deploy an ISO 27001-based security framework.</t>
-        </is>
+      <c r="J3" t="n">
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="n">
-        <v>5</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>ICT-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICT-003</t>
+          <t>Critical Systems are supported by out of date infrastructure and operating systems, resulting in numerous outages and untreatable cyber security intrusions. Current infrastructure is not architected for high availability. Lack of Disaster Recovery facilities that will meet Recovery Time and Point Objective requirements</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Critical systems are vulnerable due to outdated infrastructure and operating systems, leading to outages and security breaches, with no high-availability architecture or adequate disaster recovery.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Infrastructure Manager</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Document and Test Backup and Recovery services. Migrate systems to new Infrastructure. ISO 27001 based Framework and associated relevant controls implemented.</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -655,20 +655,20 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Migrate systems to new infrastructure and implement an ISO 27001-based security framework with tested backup and recovery services.</t>
-        </is>
+      <c r="J4" t="n">
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
         <v>5</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
